--- a/src/Tests/Templates/Contracts.xlsx
+++ b/src/Tests/Templates/Contracts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Утилита\src\Tests\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RX253\git_repository\rx-util-importdata-net-core\src\Tests\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
   <si>
     <t>Содержание</t>
   </si>
@@ -173,22 +173,13 @@
   </si>
   <si>
     <t>24.03.2025</t>
-  </si>
-  <si>
-    <t>869</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t>60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -218,10 +209,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -352,7 +339,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -479,12 +466,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -939,7 +925,7 @@
       <c r="AA1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="41">
+      <c r="A2" s="39">
         <v>675</v>
       </c>
       <c r="B2" s="7">
@@ -987,7 +973,7 @@
         <v>35</v>
       </c>
       <c r="R2" s="34">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="S2" s="36" t="s">
         <v>36</v>
@@ -1012,11 +998,11 @@
       <c r="AA2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="40">
-        <v>45525</v>
+      <c r="A3" s="40">
+        <v>869</v>
+      </c>
+      <c r="B3" s="7">
+        <v>40410</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>30</v>
@@ -1060,7 +1046,7 @@
         <v>35</v>
       </c>
       <c r="R3" s="34">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="S3" s="36" t="s">
         <v>36</v>
@@ -1082,11 +1068,11 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="40">
-        <v>45526</v>
+      <c r="A4" s="40">
+        <v>392</v>
+      </c>
+      <c r="B4" s="7">
+        <v>40410</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>30</v>
@@ -1130,7 +1116,7 @@
         <v>35</v>
       </c>
       <c r="R4" s="34">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="S4" s="36" t="s">
         <v>36</v>
@@ -1152,11 +1138,11 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="40">
-        <v>45527</v>
+      <c r="A5" s="40">
+        <v>60</v>
+      </c>
+      <c r="B5" s="7">
+        <v>40410</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>30</v>
@@ -1200,7 +1186,7 @@
         <v>35</v>
       </c>
       <c r="R5" s="34">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="S5" s="36" t="s">
         <v>36</v>

--- a/src/Tests/Templates/Contracts.xlsx
+++ b/src/Tests/Templates/Contracts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RX253\git_repository\rx-util-importdata-net-core\src\Tests\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Утилита\src\Tests\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>Содержание</t>
   </si>
@@ -173,13 +173,22 @@
   </si>
   <si>
     <t>24.03.2025</t>
+  </si>
+  <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -209,6 +218,10 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
@@ -339,7 +352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -466,11 +479,12 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -925,7 +939,7 @@
       <c r="AA1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" s="39">
+      <c r="A2" s="41">
         <v>675</v>
       </c>
       <c r="B2" s="7">
@@ -973,7 +987,7 @@
         <v>35</v>
       </c>
       <c r="R2" s="34">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="S2" s="36" t="s">
         <v>36</v>
@@ -998,11 +1012,11 @@
       <c r="AA2"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" s="40">
-        <v>869</v>
-      </c>
-      <c r="B3" s="7">
-        <v>40410</v>
+      <c r="A3" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="40">
+        <v>45525</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>30</v>
@@ -1046,7 +1060,7 @@
         <v>35</v>
       </c>
       <c r="R3" s="34">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="S3" s="36" t="s">
         <v>36</v>
@@ -1068,11 +1082,11 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="40">
-        <v>392</v>
-      </c>
-      <c r="B4" s="7">
-        <v>40410</v>
+      <c r="A4" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="40">
+        <v>45526</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>30</v>
@@ -1116,7 +1130,7 @@
         <v>35</v>
       </c>
       <c r="R4" s="34">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="S4" s="36" t="s">
         <v>36</v>
@@ -1138,11 +1152,11 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="40">
-        <v>60</v>
-      </c>
-      <c r="B5" s="7">
-        <v>40410</v>
+      <c r="A5" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="40">
+        <v>45527</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>30</v>
@@ -1186,7 +1200,7 @@
         <v>35</v>
       </c>
       <c r="R5" s="34">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="S5" s="36" t="s">
         <v>36</v>
